--- a/sample_pwa_input.xlsx
+++ b/sample_pwa_input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
   <si>
     <t>Company</t>
   </si>
@@ -69,19 +69,25 @@
     <t>Jon Smith</t>
   </si>
   <si>
+    <t>Coordinator1</t>
+  </si>
+  <si>
     <t>Firmware update</t>
   </si>
   <si>
-    <t>Firmware Update</t>
-  </si>
-  <si>
-    <t>Firmeware update</t>
+    <t>F/W Update</t>
+  </si>
+  <si>
+    <t>Firm ware update</t>
   </si>
   <si>
     <t>Inspection</t>
   </si>
   <si>
     <t>Inspecton</t>
+  </si>
+  <si>
+    <t>Commissioning</t>
   </si>
   <si>
     <t>SOP-001</t>
@@ -496,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -530,10 +536,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -553,10 +559,10 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -576,10 +582,10 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -599,10 +605,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -622,10 +628,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -645,10 +651,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -657,6 +663,26 @@
         <v>4</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
     </row>
@@ -672,22 +698,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -698,10 +724,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
@@ -715,16 +741,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -735,16 +761,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>-1</v>
@@ -755,19 +781,19 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -782,12 +808,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
